--- a/assets_cropped/Tokai Teio/transformed/manifest_edit.xlsx
+++ b/assets_cropped/Tokai Teio/transformed/manifest_edit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\TanukiProject\tanuki_app\assets_cropped\Tokai Teio\transformed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF550B4F-A092-4BD2-B5B5-E920CFB65BC8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0326647C-277B-49ED-B39E-B51E1F56636F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="8955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -677,47 +677,47 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>honey_guard_move,care_approach,negative_reaction,drag</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>honey_guard_take,offer_timeout_route_b_step2,negative_reaction,hard_landing</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>relation_watch</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>drag,window_flight</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>drag,random,window_flight,window_walk</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>drag,random,window_walk</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>random,window_perch</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>post_observe,random,window_perch</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bottle_feed_watch,random,window_perch</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>care_companion,relation_watch,random,window_perch</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>care_companion,relation_watch</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>honey_guard_move,care_approach,negative_reaction,drag</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>honey_guard_take,offer_timeout_route_b_step2,negative_reaction,hard_landing</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>relation_watch</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>drag,window_flight</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>drag,random,window_flight,window_walk</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>drag,random,window_walk</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>random,window_perch</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>care_companion,relation_watch,random,window_perch</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>post_observe,random,window_perch</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>bottle_feed_watch,random,window_perch</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1101,7 +1101,7 @@
         <v>206</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1115,7 +1115,7 @@
         <v>206</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1129,7 +1129,7 @@
         <v>206</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1143,7 +1143,7 @@
         <v>206</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1157,7 +1157,7 @@
         <v>206</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1171,7 +1171,7 @@
         <v>206</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1185,7 +1185,7 @@
         <v>206</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1255,7 +1255,7 @@
         <v>206</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1297,7 +1297,7 @@
         <v>206</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1325,7 +1325,7 @@
         <v>206</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1339,7 +1339,7 @@
         <v>206</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1353,7 +1353,7 @@
         <v>206</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1367,7 +1367,7 @@
         <v>206</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D24">
         <v>1</v>

--- a/assets_cropped/Tokai Teio/transformed/manifest_edit.xlsx
+++ b/assets_cropped/Tokai Teio/transformed/manifest_edit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\TanukiProject\tanuki_app\assets_cropped\Tokai Teio\transformed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0326647C-277B-49ED-B39E-B51E1F56636F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D012EC8A-CB59-43D9-9E36-89F903B75545}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="8955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="223">
   <si>
     <t>filename</t>
   </si>
@@ -685,14 +685,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>relation_watch</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>drag,window_flight</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>drag,random,window_flight,window_walk</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -709,15 +701,31 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>bottle_feed_watch,random,window_perch</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>care_companion,relation_watch,random,window_perch</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>care_companion,relation_watch</t>
+    <t>relation_watch,activity_chorus_finish</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>care_companion,relation_watch,random,window_perch,activity_chorus_finish</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>care_companion,relation_watch,activity_chorus_finish</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>drag,window_flight,activity_chorus_approach</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bottle_feed_watch,activity_chorus_observe</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bottle_feed_watch,random,window_perch,activity_chorus_observe</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>activity_chorus_perform</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1072,8 +1080,8 @@
       <c r="B3" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C3" t="s">
-        <v>28</v>
+      <c r="C3" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1086,8 +1094,8 @@
       <c r="B4" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C4" t="s">
-        <v>28</v>
+      <c r="C4" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1101,7 +1109,7 @@
         <v>206</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1115,7 +1123,7 @@
         <v>206</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1129,7 +1137,7 @@
         <v>206</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1143,7 +1151,7 @@
         <v>206</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1157,7 +1165,7 @@
         <v>206</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1185,7 +1193,7 @@
         <v>206</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1255,7 +1263,7 @@
         <v>206</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1297,7 +1305,7 @@
         <v>206</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1310,8 +1318,8 @@
       <c r="B20" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C20" t="s">
-        <v>207</v>
+      <c r="C20" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1325,7 +1333,7 @@
         <v>206</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1339,7 +1347,7 @@
         <v>206</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1367,7 +1375,7 @@
         <v>206</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D24">
         <v>1</v>
